--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PICOS速查" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'第三轮全文筛选'!$A$1:$L$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'第三轮全文筛选'!$A$1:$L$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L109"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4624,34 +4624,34 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D102" s="3" t="inlineStr">
         <is>
-          <t>Brandes-Aitken</t>
+          <t>Ramphal</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Maternal heart rate variability at 3-months postpartum is associated with maternal mental health and infant neurophysiology</t>
+          <t>Timing-specific associations between income-to-needs ratio and hippocampal and amygdala volumes in middle childhood: A preliminary study</t>
         </is>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Developmental Psychobiology</t>
         </is>
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>10.1038/s41598-024-68398-4</t>
+          <t>10.1002/dev.22153</t>
         </is>
       </c>
       <c r="H102" s="3" t="inlineStr">
         <is>
-          <t>Brandes-Aitken 等 - 2024 - Maternal heart rate variability at 3-months postpartum is associated with maternal mental health and.pdf</t>
+          <t>2021_Timing-specific associations between income-to-needs ratio and hippocampal.pdf</t>
         </is>
       </c>
       <c r="I102" s="2" t="n"/>
@@ -4664,34 +4664,34 @@
         <v>102</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>Simon</t>
+          <t>Brandes-Aitken</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Socioeconomic factors, stress, hair cortisol, and white matter microstructure in children</t>
+          <t>Maternal heart rate variability at 3-months postpartum is associated with maternal mental health and infant neurophysiology</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Developmental Psychobiology</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>10.1002/dev.22147</t>
+          <t>10.1038/s41598-024-68398-4</t>
         </is>
       </c>
       <c r="H103" s="3" t="inlineStr">
         <is>
-          <t>Simon 等 - 2021 - Socioeconomic factors, stress, hair cortisol, and white matter microstructure in children.pdf</t>
+          <t>Brandes-Aitken 等 - 2024 - Maternal heart rate variability at 3-months postpartum is associated with maternal mental health and.pdf</t>
         </is>
       </c>
       <c r="I103" s="2" t="n"/>
@@ -4704,34 +4704,34 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>Ursache</t>
+          <t>Simon</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Socioeconomic status, white matter, and executive function in children</t>
+          <t>Socioeconomic factors, stress, hair cortisol, and white matter microstructure in children</t>
         </is>
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>Brain and Behavior</t>
+          <t>Developmental Psychobiology</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>10.1002/brb3.531</t>
+          <t>10.1002/dev.22147</t>
         </is>
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>Ursache 等 - 2016 - Socioeconomic status, white matter, and executive function in children.pdf</t>
+          <t>Simon 等 - 2021 - Socioeconomic factors, stress, hair cortisol, and white matter microstructure in children.pdf</t>
         </is>
       </c>
       <c r="I104" s="2" t="n"/>
@@ -4744,34 +4744,34 @@
         <v>104</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>Faghiri</t>
+          <t>Ursache</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Brain Development Includes Linear and Multiple Nonlinear Trajectories: A Cross-Sectional Resting-State Functional Magnetic Resonance Imaging Study</t>
+          <t>Socioeconomic status, white matter, and executive function in children</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
         <is>
-          <t>Brain Connectivity</t>
+          <t>Brain and Behavior</t>
         </is>
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>10.1089/brain.2018.0641</t>
+          <t>10.1002/brb3.531</t>
         </is>
       </c>
       <c r="H105" s="3" t="inlineStr">
         <is>
-          <t>Faghiri 等 - 2019 - Brain development includes linear and multiple nonlinear trajectories A cross-sectional resting-sta.pdf</t>
+          <t>Ursache 等 - 2016 - Socioeconomic status, white matter, and executive function in children.pdf</t>
         </is>
       </c>
       <c r="I105" s="2" t="n"/>
@@ -4784,34 +4784,34 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>Willner</t>
+          <t>Faghiri</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Neurophysiological evidence for distinct biases in emotional face processing associated with internalizing and externalizing symptoms in children</t>
+          <t>Brain Development Includes Linear and Multiple Nonlinear Trajectories: A Cross-Sectional Resting-State Functional Magnetic Resonance Imaging Study</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
         <is>
-          <t>Biological Psychology</t>
+          <t>Brain Connectivity</t>
         </is>
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.biopsycho.2019.107829</t>
+          <t>10.1089/brain.2018.0641</t>
         </is>
       </c>
       <c r="H106" s="3" t="inlineStr">
         <is>
-          <t>Willner 等 - 2020 - Neurophysiological evidence for distinct biases in emotional face processing associated with interna.pdf</t>
+          <t>Faghiri 等 - 2019 - Brain development includes linear and multiple nonlinear trajectories A cross-sectional resting-sta.pdf</t>
         </is>
       </c>
       <c r="I106" s="2" t="n"/>
@@ -4824,34 +4824,34 @@
         <v>106</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D107" s="3" t="inlineStr">
         <is>
-          <t>Stevens</t>
+          <t>Willner</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Atypical auditory refractory periods in children from lower socio-economic status backgrounds: ERP evidence for a role of selective attention</t>
+          <t>Neurophysiological evidence for distinct biases in emotional face processing associated with internalizing and externalizing symptoms in children</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
         <is>
-          <t>International Journal of Psychophysiology</t>
+          <t>Biological Psychology</t>
         </is>
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>10.1016/j.ijpsycho.2014.06.017</t>
+          <t>10.1016/j.biopsycho.2019.107829</t>
         </is>
       </c>
       <c r="H107" s="3" t="inlineStr">
         <is>
-          <t>Stevens 等 - 2015 - Atypical auditory refractory periods in children from lower socio-economic status backgrounds ERP e.pdf</t>
+          <t>Willner 等 - 2020 - Neurophysiological evidence for distinct biases in emotional face processing associated with interna.pdf</t>
         </is>
       </c>
       <c r="I107" s="2" t="n"/>
@@ -4864,34 +4864,34 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>Lewinn</t>
+          <t>Stevens</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Sample composition alters associations between age and brain structure</t>
+          <t>Atypical auditory refractory periods in children from lower socio-economic status backgrounds: ERP evidence for a role of selective attention</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
         <is>
-          <t>Nature Communications</t>
+          <t>International Journal of Psychophysiology</t>
         </is>
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>10.1038/s41467-017-00908-7</t>
+          <t>10.1016/j.ijpsycho.2014.06.017</t>
         </is>
       </c>
       <c r="H108" s="3" t="inlineStr">
         <is>
-          <t>LeWinn 等 - 2017 - Sample composition alters associations between age and brain structure.pdf</t>
+          <t>Stevens 等 - 2015 - Atypical auditory refractory periods in children from lower socio-economic status backgrounds ERP e.pdf</t>
         </is>
       </c>
       <c r="I108" s="2" t="n"/>
@@ -4904,34 +4904,34 @@
         <v>108</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>2010</v>
+        <v>2017</v>
       </c>
       <c r="D109" s="3" t="inlineStr">
         <is>
-          <t>Lange</t>
+          <t>Lewinn</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Associations between IQ, total and regional brain volumes, and demography in a large normative sample of healthy children and adolescents</t>
+          <t>Sample composition alters associations between age and brain structure</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>Developmental Neuropsychology</t>
+          <t>Nature Communications</t>
         </is>
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>10.1080/87565641003696833</t>
+          <t>10.1038/s41467-017-00908-7</t>
         </is>
       </c>
       <c r="H109" s="3" t="inlineStr">
         <is>
-          <t>Lange 等 - 2010 - Associations between IQ, total and regional brain volumes, and demography in a large normative sampl.pdf</t>
+          <t>LeWinn 等 - 2017 - Sample composition alters associations between age and brain structure.pdf</t>
         </is>
       </c>
       <c r="I109" s="2" t="n"/>
@@ -4939,9 +4939,49 @@
       <c r="K109" s="4" t="n"/>
       <c r="L109" s="4" t="n"/>
     </row>
+    <row r="110" ht="32" customHeight="1">
+      <c r="A110" s="2" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>132</v>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>2010</v>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>Lange</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Associations between IQ, total and regional brain volumes, and demography in a large normative sample of healthy children and adolescents</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="inlineStr">
+        <is>
+          <t>Developmental Neuropsychology</t>
+        </is>
+      </c>
+      <c r="G110" s="3" t="inlineStr">
+        <is>
+          <t>10.1080/87565641003696833</t>
+        </is>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>Lange 等 - 2010 - Associations between IQ, total and regional brain volumes, and demography in a large normative sampl.pdf</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="4" t="n"/>
+      <c r="L110" s="4" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L109"/>
-  <conditionalFormatting sqref="A2:L109">
+  <autoFilter ref="A1:L110"/>
+  <conditionalFormatting sqref="A2:L110">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$I2="纳入"</formula>
     </cfRule>
@@ -4953,10 +4993,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="I2:I109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"纳入,排除,不确定"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J110" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"E1-年龄不符,E2-暴露不符,E3-无神经指标,E4-综述/protocol,E5-非英文,E6-全文不可及,E7-样本重复,E8-其他"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5009,7 +5049,7 @@
         </is>
       </c>
       <c r="B3" s="7">
-        <f>COUNTA(第三轮全文筛选!A2:A109)</f>
+        <f>COUNTA(第三轮全文筛选!A2:A110)</f>
         <v/>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -5025,7 +5065,7 @@
         </is>
       </c>
       <c r="B4" s="7">
-        <f>COUNTA(第三轮全文筛选!I2:I109)</f>
+        <f>COUNTA(第三轮全文筛选!I2:I110)</f>
         <v/>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -5074,7 +5114,7 @@
         </is>
       </c>
       <c r="B8" s="7">
-        <f>COUNTIF(第三轮全文筛选!I$2:I$109,"纳入")</f>
+        <f>COUNTIF(第三轮全文筛选!I$2:I$110,"纳入")</f>
         <v/>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -5090,7 +5130,7 @@
         </is>
       </c>
       <c r="B9" s="7">
-        <f>COUNTIF(第三轮全文筛选!I$2:I$109,"排除")</f>
+        <f>COUNTIF(第三轮全文筛选!I$2:I$110,"排除")</f>
         <v/>
       </c>
       <c r="C9" s="7" t="inlineStr"/>
@@ -5102,7 +5142,7 @@
         </is>
       </c>
       <c r="B10" s="7">
-        <f>COUNTIF(第三轮全文筛选!I$2:I$109,"不确定")</f>
+        <f>COUNTIF(第三轮全文筛选!I$2:I$110,"不确定")</f>
         <v/>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -5132,7 +5172,7 @@
         </is>
       </c>
       <c r="B13" s="7">
-        <f>COUNTIF(第三轮全文筛选!J$2:J$109,"E1-年龄不符")</f>
+        <f>COUNTIF(第三轮全文筛选!J$2:J$110,"E1-年龄不符")</f>
         <v/>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -5148,7 +5188,7 @@
         </is>
       </c>
       <c r="B14" s="7">
-        <f>COUNTIF(第三轮全文筛选!J$2:J$109,"E2-暴露不符")</f>
+        <f>COUNTIF(第三轮全文筛选!J$2:J$110,"E2-暴露不符")</f>
         <v/>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -5164,7 +5204,7 @@
         </is>
       </c>
       <c r="B15" s="7">
-        <f>COUNTIF(第三轮全文筛选!J$2:J$109,"E3-无神经指标")</f>
+        <f>COUNTIF(第三轮全文筛选!J$2:J$110,"E3-无神经指标")</f>
         <v/>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -5180,7 +5220,7 @@
         </is>
       </c>
       <c r="B16" s="7">
-        <f>COUNTIF(第三轮全文筛选!J$2:J$109,"E4-综述/protocol")</f>
+        <f>COUNTIF(第三轮全文筛选!J$2:J$110,"E4-综述/protocol")</f>
         <v/>
       </c>
       <c r="C16" s="7" t="inlineStr">
@@ -5196,7 +5236,7 @@
         </is>
       </c>
       <c r="B17" s="7">
-        <f>COUNTIF(第三轮全文筛选!J$2:J$109,"E5-非英文")</f>
+        <f>COUNTIF(第三轮全文筛选!J$2:J$110,"E5-非英文")</f>
         <v/>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -5212,7 +5252,7 @@
         </is>
       </c>
       <c r="B18" s="7">
-        <f>COUNTIF(第三轮全文筛选!J$2:J$109,"E6-全文不可及")</f>
+        <f>COUNTIF(第三轮全文筛选!J$2:J$110,"E6-全文不可及")</f>
         <v/>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -5228,7 +5268,7 @@
         </is>
       </c>
       <c r="B19" s="7">
-        <f>COUNTIF(第三轮全文筛选!J$2:J$109,"E7-样本重复")</f>
+        <f>COUNTIF(第三轮全文筛选!J$2:J$110,"E7-样本重复")</f>
         <v/>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -5244,7 +5284,7 @@
         </is>
       </c>
       <c r="B20" s="7">
-        <f>COUNTIF(第三轮全文筛选!J$2:J$109,"E8-其他")</f>
+        <f>COUNTIF(第三轮全文筛选!J$2:J$110,"E8-其他")</f>
         <v/>
       </c>
       <c r="C20" s="7" t="inlineStr">

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -654,9 +654,13 @@
           <t>Hair 等 - 2015 - Association of child poverty, brain development, and academic achievement.pdf</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n"/>
-      <c r="K2" s="4" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr"/>
       <c r="L2" s="4" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
@@ -694,9 +698,13 @@
           <t>Myers 等 - 2014 - White matter morphometric changes uniquely predict children’s reading acquisition.pdf</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="4" t="n"/>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
       <c r="L3" s="4" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
@@ -734,9 +742,21 @@
           <t>Tarullo 等 - 2024 - Neonatal physical growth predicts electroencephalography power in rural south african children.pdf</t>
         </is>
       </c>
-      <c r="I4" s="2" t="n"/>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="4" t="n"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L4" s="4" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
@@ -774,9 +794,21 @@
           <t>Wu 等 - 2023 - Cerebellar growth, volume and diffusivity in children cooled for neonatal encephalopathy without cer.pdf</t>
         </is>
       </c>
-      <c r="I5" s="2" t="n"/>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="4" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L5" s="4" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
@@ -814,9 +846,13 @@
           <t>Wienke和Mathes - 2024 - Socioeconomic inequalities affect brain responses of infants growing up in Germany.pdf</t>
         </is>
       </c>
-      <c r="I6" s="2" t="n"/>
-      <c r="J6" s="2" t="n"/>
-      <c r="K6" s="4" t="n"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
@@ -854,10 +890,26 @@
           <t>Troller-Renfree 等 - 2021 - Feasibility of assessing brain activity using mobile, in-home collection of electroencephalography.pdf</t>
         </is>
       </c>
-      <c r="I7" s="2" t="n"/>
-      <c r="J7" s="2" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>原序号45</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="2" t="n">
@@ -894,9 +946,13 @@
           <t>Wijeakumar 等 - 2019 - Early adversity in rural India impacts the brain networks underlying visual working memory.pdf</t>
         </is>
       </c>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="4" t="n"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
       <c r="L8" s="4" t="n"/>
     </row>
     <row r="9" ht="32" customHeight="1">
@@ -934,9 +990,13 @@
           <t>Salzwedel 等 - 2016 - Thalamocortical functional connectivity and behavioral disruptions in neonates with prenatal cocaine.pdf</t>
         </is>
       </c>
-      <c r="I9" s="2" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="4" t="n"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
       <c r="L9" s="4" t="n"/>
     </row>
     <row r="10" ht="32" customHeight="1">
@@ -974,9 +1034,13 @@
           <t>Stiver 等 - 2015 - Maternal postsecondary education associated with improved cerebellar growth after preterm birth.pdf</t>
         </is>
       </c>
-      <c r="I10" s="2" t="n"/>
-      <c r="J10" s="2" t="n"/>
-      <c r="K10" s="4" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
       <c r="L10" s="4" t="n"/>
     </row>
     <row r="11" ht="32" customHeight="1">
@@ -1014,9 +1078,21 @@
           <t>Prasad - 2005 - Cognitive and neuroimaging findings in physically abused preschoolers.pdf</t>
         </is>
       </c>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="4" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L11" s="4" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
@@ -1054,9 +1130,21 @@
           <t>Moses-Kolko 等 - 2021 - Reduced postpartum hippocampal volume is associated with positive mother-infant caregiving behavior.pdf</t>
         </is>
       </c>
-      <c r="I12" s="2" t="n"/>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="4" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L12" s="4" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
@@ -1094,9 +1182,21 @@
           <t>Benavente-Fernández 等 - 2020 - Socioeconomic status and brain injury in children born preterm Modifying neurodevelopmental outcome.pdf</t>
         </is>
       </c>
-      <c r="I13" s="2" t="n"/>
-      <c r="J13" s="2" t="n"/>
-      <c r="K13" s="4" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>教育变量无独立效应</t>
+        </is>
+      </c>
       <c r="L13" s="4" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
@@ -1134,9 +1234,13 @@
           <t>Brito 等 - 2020 - Associations among the home language environment and neural activity during infancy.pdf</t>
         </is>
       </c>
-      <c r="I14" s="2" t="n"/>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="4" t="n"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4" t="n"/>
     </row>
     <row r="15" ht="32" customHeight="1">
@@ -1174,9 +1278,21 @@
           <t>Wu 等 - 2016 - Clinical electroencephalographic biomarker for impending epilepsy in asymptomatic tuberous sclerosis.pdf</t>
         </is>
       </c>
-      <c r="I15" s="2" t="n"/>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="4" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>教育变量无独立效应</t>
+        </is>
+      </c>
       <c r="L15" s="4" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1">
@@ -1214,9 +1330,13 @@
           <t>Mckinnon 等 - 2023 - Association of Preterm Birth and Socioeconomic Status With Neonatal Brain Structure.pdf</t>
         </is>
       </c>
-      <c r="I16" s="2" t="n"/>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="4" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
@@ -1254,9 +1374,13 @@
           <t>Troller-Renfree 等 - 2022 - The impact of a poverty reduction intervention on infant brain activity.pdf</t>
         </is>
       </c>
-      <c r="I17" s="2" t="n"/>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="4" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
@@ -1294,9 +1418,21 @@
           <t>Katus 等 - 2020 - ERP markers are associated with neurodevelopmental outcomes in 1–5 month old infants in rural africa.pdf</t>
         </is>
       </c>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="4" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L18" s="4" t="n"/>
     </row>
     <row r="19" ht="32" customHeight="1">
@@ -1334,9 +1470,21 @@
           <t>Oldenburg 等 - 2020 - Genetic and epigenetic factors and early life inflammation as predictors of neurodevelopmental outco.pdf</t>
         </is>
       </c>
-      <c r="I19" s="2" t="n"/>
-      <c r="J19" s="2" t="n"/>
-      <c r="K19" s="4" t="n"/>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>教育变量无独立效应</t>
+        </is>
+      </c>
       <c r="L19" s="4" t="n"/>
     </row>
     <row r="20" ht="32" customHeight="1">
@@ -1374,7 +1522,11 @@
           <t>Zhu 等 - 2023 - Trajectories of brain volumes in young children are associated with maternal education.pdf</t>
         </is>
       </c>
-      <c r="I20" s="2" t="n"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
@@ -1414,9 +1566,13 @@
           <t>Konrad 等 - 2024 - Socioeconomic status moderates associations between hippocampal development and cognition in preterm.pdf</t>
         </is>
       </c>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="4" t="n"/>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4" t="n"/>
     </row>
     <row r="22" ht="32" customHeight="1">
@@ -1454,9 +1610,13 @@
           <t>Triplett 等 - 2022 - Association of prenatal exposure to early-life adversity with neonatal brain volumes at birth.pdf</t>
         </is>
       </c>
-      <c r="I22" s="2" t="n"/>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="4" t="n"/>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
@@ -1494,9 +1654,13 @@
           <t>Moriguchi和Shinohara - 2019 - Socioeconomic disparity in prefrontal development during early childhood.pdf</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n"/>
-      <c r="J23" s="2" t="n"/>
-      <c r="K23" s="4" t="n"/>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
       <c r="L23" s="4" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
@@ -1534,9 +1698,13 @@
           <t>Demir-Lira 等 - 2021 - Neurocognitive basis of deductive reasoning in children varies with parental education.pdf</t>
         </is>
       </c>
-      <c r="I24" s="2" t="n"/>
-      <c r="J24" s="2" t="n"/>
-      <c r="K24" s="4" t="n"/>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr"/>
       <c r="L24" s="4" t="n"/>
     </row>
     <row r="25" ht="32" customHeight="1">
@@ -1574,9 +1742,13 @@
           <t>Brito 等 - 2016 - Associations among family socioeconomic status, EEG power at birth, and cognitive skills during infa.pdf</t>
         </is>
       </c>
-      <c r="I25" s="2" t="n"/>
-      <c r="J25" s="2" t="n"/>
-      <c r="K25" s="4" t="n"/>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
       <c r="L25" s="4" t="n"/>
     </row>
     <row r="26" ht="32" customHeight="1">
@@ -1614,10 +1786,26 @@
           <t>Romeo 等 - 2018 - Language exposure relates to structural neural connectivity in childhood.pdf</t>
         </is>
       </c>
-      <c r="I26" s="2" t="n"/>
-      <c r="J26" s="2" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>教育变量无独立效应</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>原序号63</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="2" t="n">
@@ -1654,9 +1842,21 @@
           <t>Ewell 等 - 2023 - Emotion regulation and reactivity are associated with cortical thickness in early to mid-childhood.pdf</t>
         </is>
       </c>
-      <c r="I27" s="2" t="n"/>
-      <c r="J27" s="2" t="n"/>
-      <c r="K27" s="4" t="n"/>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L27" s="4" t="n"/>
     </row>
     <row r="28" ht="32" customHeight="1">
@@ -1694,9 +1894,13 @@
           <t>Leonard 等 - 2019 - Associations between cortical thickness and reasoning differ by socioeconomic status in development.pdf</t>
         </is>
       </c>
-      <c r="I28" s="2" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="4" t="n"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="4" t="inlineStr"/>
       <c r="L28" s="4" t="n"/>
     </row>
     <row r="29" ht="32" customHeight="1">
@@ -1734,9 +1938,13 @@
           <t>Ramphal 等 - 2020 - Brain connectivity and socioeconomic status at birth and externalizing symptoms at age 2 years.pdf</t>
         </is>
       </c>
-      <c r="I29" s="2" t="n"/>
-      <c r="J29" s="2" t="n"/>
-      <c r="K29" s="4" t="n"/>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr"/>
       <c r="L29" s="4" t="n"/>
     </row>
     <row r="30" ht="32" customHeight="1">
@@ -1774,9 +1982,13 @@
           <t>Patterson 等 - 2025 - Prenatal household income instability and infant subcortical brain volumes.pdf</t>
         </is>
       </c>
-      <c r="I30" s="2" t="n"/>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="4" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
       <c r="L30" s="4" t="n"/>
     </row>
     <row r="31" ht="32" customHeight="1">
@@ -1814,9 +2026,21 @@
           <t>Woodward 等 - 2023 - Factors associated with MRI success in children cooled for neonatal encephalopathy and controls.pdf</t>
         </is>
       </c>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="4" t="n"/>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L31" s="4" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
@@ -1854,9 +2078,13 @@
           <t>Turesky 等 - 2024 - Brain morphometry and chronic inflammation in bangladeshi children growing up in extreme poverty.pdf</t>
         </is>
       </c>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="4" t="n"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
       <c r="L32" s="4" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
@@ -1894,9 +2122,13 @@
           <t>Farah 等 - 2021 - Randomized manipulation of early cognitive experience impacts adult brain structure.pdf</t>
         </is>
       </c>
-      <c r="I33" s="2" t="n"/>
-      <c r="J33" s="2" t="n"/>
-      <c r="K33" s="4" t="n"/>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
       <c r="L33" s="4" t="n"/>
     </row>
     <row r="34" ht="32" customHeight="1">
@@ -1934,9 +2166,13 @@
           <t>Ferschmann 等 - 2024 - The importance of timing of socioeconomic disadvantage throughout development for depressive symptom.pdf</t>
         </is>
       </c>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="4" t="n"/>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr"/>
       <c r="L34" s="4" t="n"/>
     </row>
     <row r="35" ht="32" customHeight="1">
@@ -1974,9 +2210,13 @@
           <t>2023_The Association BetweenMaternal Cortisol and InfantAmygdala Volume.pdf</t>
         </is>
       </c>
-      <c r="I35" s="2" t="n"/>
-      <c r="J35" s="2" t="n"/>
-      <c r="K35" s="4" t="n"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
       <c r="L35" s="4" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
@@ -2014,9 +2254,13 @@
           <t>St. John 等 - 2019 - Socioeconomic status and neural processing of a gono-go task in preschoolers An assessment of the.pdf</t>
         </is>
       </c>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="4" t="n"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr"/>
       <c r="L36" s="4" t="n"/>
     </row>
     <row r="37" ht="32" customHeight="1">
@@ -2054,9 +2298,13 @@
           <t>Dufford 等 - 2020 - Prospective associations, longitudinal patterns of childhood socioeconomic status, and white matter.pdf</t>
         </is>
       </c>
-      <c r="I37" s="2" t="n"/>
-      <c r="J37" s="2" t="n"/>
-      <c r="K37" s="4" t="n"/>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="4" t="inlineStr"/>
       <c r="L37" s="4" t="n"/>
     </row>
     <row r="38" ht="32" customHeight="1">
@@ -2094,9 +2342,13 @@
           <t>Pellowski 等 - 2023 - Maternal perinatal depression and child brain structure at 2-3 years in a south african birth cohort.pdf</t>
         </is>
       </c>
-      <c r="I38" s="2" t="n"/>
-      <c r="J38" s="2" t="n"/>
-      <c r="K38" s="4" t="n"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="4" t="inlineStr"/>
       <c r="L38" s="4" t="n"/>
     </row>
     <row r="39" ht="32" customHeight="1">
@@ -2134,9 +2386,13 @@
           <t>Tomalski 等 - 2013 - Socioeconomic status and functional brain development – associations in early infancy.pdf</t>
         </is>
       </c>
-      <c r="I39" s="2" t="n"/>
-      <c r="J39" s="2" t="n"/>
-      <c r="K39" s="4" t="n"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
       <c r="L39" s="4" t="n"/>
     </row>
     <row r="40" ht="32" customHeight="1">
@@ -2174,9 +2430,13 @@
           <t>Hutton 等 - 2017 - Shared reading quality and brain activation during story listening in preschool-age children.pdf</t>
         </is>
       </c>
-      <c r="I40" s="2" t="n"/>
-      <c r="J40" s="2" t="n"/>
-      <c r="K40" s="4" t="n"/>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr"/>
       <c r="L40" s="4" t="n"/>
     </row>
     <row r="41" ht="32" customHeight="1">
@@ -2214,9 +2474,13 @@
           <t>Gao 等 - 2015 - Functional network development during the first year Relative sequence and socioeconomic correlatio.pdf</t>
         </is>
       </c>
-      <c r="I41" s="2" t="n"/>
-      <c r="J41" s="2" t="n"/>
-      <c r="K41" s="4" t="n"/>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr"/>
       <c r="L41" s="4" t="n"/>
     </row>
     <row r="42" ht="32" customHeight="1">
@@ -2254,9 +2518,13 @@
           <t>Lean 等 - 2022 - Prenatal exposure to maternal social disadvantage and psychosocial stress and neonatal white matter.pdf</t>
         </is>
       </c>
-      <c r="I42" s="2" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="4" t="n"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
       <c r="L42" s="4" t="n"/>
     </row>
     <row r="43" ht="32" customHeight="1">
@@ -2294,9 +2562,13 @@
           <t>Lean 等 - 2022 - Prenatal exposure to maternal social disadvantage and psychosocial stress and neonatal white matter.pdf</t>
         </is>
       </c>
-      <c r="I43" s="2" t="n"/>
-      <c r="J43" s="2" t="n"/>
-      <c r="K43" s="4" t="n"/>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr"/>
       <c r="L43" s="4" t="n"/>
     </row>
     <row r="44" ht="32" customHeight="1">
@@ -2334,9 +2606,13 @@
           <t>Ozernov-Palchik 等 - 2019 - The relationship between socioeconomic status and white matter microstructure in pre-reading childre.pdf</t>
         </is>
       </c>
-      <c r="I44" s="2" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="4" t="n"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr"/>
       <c r="L44" s="4" t="n"/>
     </row>
     <row r="45" ht="32" customHeight="1">
@@ -2374,9 +2650,13 @@
           <t>Hanson 等 - 2013 - Family poverty affects the rate of human infant brain growth.pdf</t>
         </is>
       </c>
-      <c r="I45" s="2" t="n"/>
-      <c r="J45" s="2" t="n"/>
-      <c r="K45" s="4" t="n"/>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr"/>
       <c r="L45" s="4" t="n"/>
     </row>
     <row r="46" ht="32" customHeight="1">
@@ -2414,9 +2694,13 @@
           <t>Sandre 等 - 2024 - Prenatal family income, but not parental education, is associated with resting brain activity in 1-m.pdf</t>
         </is>
       </c>
-      <c r="I46" s="2" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="4" t="n"/>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
       <c r="L46" s="4" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
@@ -2454,10 +2738,26 @@
           <t>Su 等 - 2021 - Effects of socioeconomic status in predicting reading outcomes for children The mediation of spoken.pdf</t>
         </is>
       </c>
-      <c r="I47" s="2" t="n"/>
-      <c r="J47" s="2" t="n"/>
-      <c r="K47" s="4" t="n"/>
-      <c r="L47" s="4" t="n"/>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>原序号99</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="2" t="n">
@@ -2494,9 +2794,13 @@
           <t>Cantiani 等 - 2019 - Oscillatory gamma activity mediates the pathway from socioeconomic status to language acquisition in.pdf</t>
         </is>
       </c>
-      <c r="I48" s="2" t="n"/>
-      <c r="J48" s="2" t="n"/>
-      <c r="K48" s="4" t="n"/>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
       <c r="L48" s="4" t="n"/>
     </row>
     <row r="49" ht="32" customHeight="1">
@@ -2534,9 +2838,13 @@
           <t>Hampton Wray 等 - 2017 - Development of selective attention in preschool-age children from lower socioeconomic status backgro.pdf</t>
         </is>
       </c>
-      <c r="I49" s="2" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="4" t="n"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
       <c r="L49" s="4" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
@@ -2574,9 +2882,13 @@
           <t>Luby 等 - 2016 - Breastfeeding and childhood IQ the mediating role of gray matter volume.pdf</t>
         </is>
       </c>
-      <c r="I50" s="2" t="n"/>
-      <c r="J50" s="2" t="n"/>
-      <c r="K50" s="4" t="n"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
       <c r="L50" s="4" t="n"/>
     </row>
     <row r="51" ht="32" customHeight="1">
@@ -2614,9 +2926,21 @@
           <t>Hutton 等 - 2015 - Home reading environment and brain activation in preschool children listening to stories.pdf</t>
         </is>
       </c>
-      <c r="I51" s="2" t="n"/>
-      <c r="J51" s="2" t="n"/>
-      <c r="K51" s="4" t="n"/>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L51" s="4" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
@@ -2654,9 +2978,13 @@
           <t>Kim 等 - 2017 - Socioeconomic disadvantage, neural responses to infant emotions, and emotional availability among fi.pdf</t>
         </is>
       </c>
-      <c r="I52" s="2" t="n"/>
-      <c r="J52" s="2" t="n"/>
-      <c r="K52" s="4" t="n"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr"/>
       <c r="L52" s="4" t="n"/>
     </row>
     <row r="53" ht="32" customHeight="1">
@@ -2694,10 +3022,18 @@
           <t>Jensen 等 - 2021 - Associations of socioeconomic and other environmental factors with early brain development in bangla.pdf</t>
         </is>
       </c>
-      <c r="I53" s="2" t="n"/>
-      <c r="J53" s="2" t="n"/>
-      <c r="K53" s="4" t="n"/>
-      <c r="L53" s="4" t="n"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>原序号106</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="32" customHeight="1">
       <c r="A54" s="2" t="n">
@@ -2734,10 +3070,18 @@
           <t>Neukomm 等 - 2022 - Perioperative course and socioeconomic status predict long-term neurodevelopment better than periope.pdf</t>
         </is>
       </c>
-      <c r="I54" s="2" t="n"/>
-      <c r="J54" s="2" t="n"/>
-      <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>原序号107</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="2" t="n">
@@ -2774,9 +3118,21 @@
           <t>Mathieson 等 - 2024 - EEG background activity, seizure burden and early childhood outcomes in neonatal encephalopathy in u.pdf</t>
         </is>
       </c>
-      <c r="I55" s="2" t="n"/>
-      <c r="J55" s="2" t="n"/>
-      <c r="K55" s="4" t="n"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L55" s="4" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
@@ -2814,9 +3170,21 @@
           <t>Sheinkopf 等 - 2009 - Functional MRI and response inhibition in children exposed to cocaine in utero.pdf</t>
         </is>
       </c>
-      <c r="I56" s="2" t="n"/>
-      <c r="J56" s="2" t="n"/>
-      <c r="K56" s="4" t="n"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L56" s="4" t="n"/>
     </row>
     <row r="57" ht="32" customHeight="1">
@@ -2854,9 +3222,13 @@
           <t>Pierce 等 - 2021 - Associations between maternal stress, early language behaviors, and infant electroencephalography du.pdf</t>
         </is>
       </c>
-      <c r="I57" s="2" t="n"/>
-      <c r="J57" s="2" t="n"/>
-      <c r="K57" s="4" t="n"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr"/>
       <c r="L57" s="4" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
@@ -2894,9 +3266,21 @@
           <t>Lloyd-Fox 等 - 2014 - Functional near infrared spectroscopy (fNIRS) to assess cognitive function in infants in rural afric.pdf</t>
         </is>
       </c>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="4" t="n"/>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L58" s="4" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
@@ -2934,9 +3318,13 @@
           <t>Lloyd-Fox 等 - 2019 - Habituation and novelty detection fNIRS brain responses in 5- and 8-month-old infants the Gambia an.pdf</t>
         </is>
       </c>
-      <c r="I59" s="2" t="n"/>
-      <c r="J59" s="2" t="n"/>
-      <c r="K59" s="4" t="n"/>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr"/>
       <c r="L59" s="4" t="n"/>
     </row>
     <row r="60" ht="32" customHeight="1">
@@ -2974,10 +3362,18 @@
           <t>Turesky 等 - 2020 - Relating anthropometric indicators to brain structure in 2-month-old bangladeshi infants growing up.pdf</t>
         </is>
       </c>
-      <c r="I60" s="2" t="n"/>
-      <c r="J60" s="2" t="n"/>
-      <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>原序号103</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="2" t="n">
@@ -3014,9 +3410,13 @@
           <t>Chajes 等 - 2022 - Examining the role of socioeconomic status and maternal sensitivity in predicting functional brain n.pdf</t>
         </is>
       </c>
-      <c r="I61" s="2" t="n"/>
-      <c r="J61" s="2" t="n"/>
-      <c r="K61" s="4" t="n"/>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr"/>
       <c r="L61" s="4" t="n"/>
     </row>
     <row r="62" ht="32" customHeight="1">
@@ -3054,9 +3454,13 @@
           <t>Barch 等 - 2022 - Early childhood socioeconomic status and cognitive and adaptive outcomes at the transition to adulth.pdf</t>
         </is>
       </c>
-      <c r="I62" s="2" t="n"/>
-      <c r="J62" s="2" t="n"/>
-      <c r="K62" s="4" t="n"/>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr"/>
       <c r="L62" s="4" t="n"/>
     </row>
     <row r="63" ht="32" customHeight="1">
@@ -3094,9 +3498,13 @@
           <t>Perdue 等 - 2019 - Using functional near-infrared spectroscopy to assess social information processing in poor urban ba.pdf</t>
         </is>
       </c>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="4" t="n"/>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr"/>
       <c r="L63" s="4" t="n"/>
     </row>
     <row r="64" ht="32" customHeight="1">
@@ -3134,9 +3542,13 @@
           <t>2025_Age-related patternsof restingEEG power in infancy.pdf</t>
         </is>
       </c>
-      <c r="I64" s="2" t="n"/>
-      <c r="J64" s="2" t="n"/>
-      <c r="K64" s="4" t="n"/>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr"/>
       <c r="L64" s="4" t="n"/>
     </row>
     <row r="65" ht="32" customHeight="1">
@@ -3174,9 +3586,13 @@
           <t>Turesky 等 - 2022 - Home language and literacy environment and its relationship to socioeconomic status and white matter.pdf</t>
         </is>
       </c>
-      <c r="I65" s="2" t="n"/>
-      <c r="J65" s="2" t="n"/>
-      <c r="K65" s="4" t="n"/>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="4" t="inlineStr"/>
       <c r="L65" s="4" t="n"/>
     </row>
     <row r="66" ht="32" customHeight="1">
@@ -3214,10 +3630,22 @@
           <t>Di Lonardo Burr 等 - 2024 - Longitudinal assessments of functional near-infrared spectroscopy background functional connectivity.pdf</t>
         </is>
       </c>
-      <c r="I66" s="2" t="n"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="n"/>
-      <c r="K66" s="4" t="n"/>
-      <c r="L66" s="4" t="n"/>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>E7参照错误（非重复文献），需全文核查父母教育是否独立报告</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>原序号73</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="32" customHeight="1">
       <c r="A67" s="2" t="n">
@@ -3254,9 +3682,21 @@
           <t>Tooley 等 - 2024 - Prenatal environment is associated with the pace of cortical network development over the first thre.pdf</t>
         </is>
       </c>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="4" t="n"/>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>同#68（正式发表版）</t>
+        </is>
+      </c>
       <c r="L67" s="4" t="n"/>
     </row>
     <row r="68" ht="32" customHeight="1">
@@ -3294,9 +3734,13 @@
           <t>Spann 等 - 2020 - Prenatal socioeconomic status and social support are associated with neonatal brain morphology, todd.pdf</t>
         </is>
       </c>
-      <c r="I68" s="2" t="n"/>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="4" t="n"/>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="4" t="inlineStr"/>
       <c r="L68" s="4" t="n"/>
     </row>
     <row r="69" ht="32" customHeight="1">
@@ -3334,9 +3778,13 @@
           <t>Tooley 等 - 2024 - Prenatal environment is associated with the pace of cortical network development over the first thre.pdf</t>
         </is>
       </c>
-      <c r="I69" s="2" t="n"/>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" s="4" t="n"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="4" t="inlineStr"/>
       <c r="L69" s="4" t="n"/>
     </row>
     <row r="70" ht="32" customHeight="1">
@@ -3374,9 +3822,13 @@
           <t>Betancourt 等 - 2016 - Effect of socioeconomic status ( SES ) disparity on ne.pdf</t>
         </is>
       </c>
-      <c r="I70" s="2" t="n"/>
-      <c r="J70" s="2" t="n"/>
-      <c r="K70" s="4" t="n"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="4" t="inlineStr"/>
       <c r="L70" s="4" t="n"/>
     </row>
     <row r="71" ht="32" customHeight="1">
@@ -3414,9 +3866,13 @@
           <t>Barch 等 - 2016 - Effect of hippocampal and amygdala connectivity on the relationship between preschool poverty and sc.pdf</t>
         </is>
       </c>
-      <c r="I71" s="2" t="n"/>
-      <c r="J71" s="2" t="n"/>
-      <c r="K71" s="4" t="n"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr"/>
       <c r="L71" s="4" t="n"/>
     </row>
     <row r="72" ht="32" customHeight="1">
@@ -3454,9 +3910,13 @@
           <t>Otero - 1997 - Poverty, cultural disadvantage and brain development a study of pre-school children in Mexico.pdf</t>
         </is>
       </c>
-      <c r="I72" s="2" t="n"/>
-      <c r="J72" s="2" t="n"/>
-      <c r="K72" s="4" t="n"/>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="4" t="inlineStr"/>
       <c r="L72" s="4" t="n"/>
     </row>
     <row r="73" ht="32" customHeight="1">
@@ -3494,9 +3954,13 @@
           <t>Maguire和Schneider - 2019 - Socioeconomic status related differences in resting state EEG activity correspond to differences in.pdf</t>
         </is>
       </c>
-      <c r="I73" s="2" t="n"/>
-      <c r="J73" s="2" t="n"/>
-      <c r="K73" s="4" t="n"/>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr"/>
       <c r="L73" s="4" t="n"/>
     </row>
     <row r="74" ht="32" customHeight="1">
@@ -3534,9 +3998,13 @@
           <t>Gonzalez 等 - 2020 - Positive economic, psychosocial, and physiological ecologies predict brain structure and cognitive p.pdf</t>
         </is>
       </c>
-      <c r="I74" s="2" t="n"/>
-      <c r="J74" s="2" t="n"/>
-      <c r="K74" s="4" t="n"/>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="4" t="inlineStr"/>
       <c r="L74" s="4" t="n"/>
     </row>
     <row r="75" ht="32" customHeight="1">
@@ -3574,9 +4042,13 @@
           <t>Lurie 等 - 2024 - Cognitive stimulation as a mechanism linking socioeconomic status and neural function supporting wor.pdf</t>
         </is>
       </c>
-      <c r="I75" s="2" t="n"/>
-      <c r="J75" s="2" t="n"/>
-      <c r="K75" s="4" t="n"/>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="4" t="inlineStr"/>
       <c r="L75" s="4" t="n"/>
     </row>
     <row r="76" ht="32" customHeight="1">
@@ -3614,9 +4086,13 @@
           <t>Shephard 等 - 2019 - Effects of maternal psychopathology and education level on neurocognitive development in infants of.pdf</t>
         </is>
       </c>
-      <c r="I76" s="2" t="n"/>
-      <c r="J76" s="2" t="n"/>
-      <c r="K76" s="4" t="n"/>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr"/>
       <c r="L76" s="4" t="n"/>
     </row>
     <row r="77" ht="32" customHeight="1">
@@ -3654,9 +4130,21 @@
           <t>Lloyd-Fox 等 - 2017 - Cortical specialisation to social stimuli from the first days to the second year of life A rural ga.pdf</t>
         </is>
       </c>
-      <c r="I77" s="2" t="n"/>
-      <c r="J77" s="2" t="n"/>
-      <c r="K77" s="4" t="n"/>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L77" s="4" t="n"/>
     </row>
     <row r="78" ht="32" customHeight="1">
@@ -3694,9 +4182,13 @@
           <t>Luby 等 - 2013 - The effects of poverty on childhood brain development the mediating effect of caregiving and stress.pdf</t>
         </is>
       </c>
-      <c r="I78" s="2" t="n"/>
-      <c r="J78" s="2" t="n"/>
-      <c r="K78" s="4" t="n"/>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="4" t="inlineStr"/>
       <c r="L78" s="4" t="n"/>
     </row>
     <row r="79" ht="32" customHeight="1">
@@ -3734,9 +4226,13 @@
           <t>Conejero 等 - 2018 - Frontal theta activation associated with error detection in toddlers influence of familial socioeco.pdf</t>
         </is>
       </c>
-      <c r="I79" s="2" t="n"/>
-      <c r="J79" s="2" t="n"/>
-      <c r="K79" s="4" t="n"/>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="4" t="inlineStr"/>
       <c r="L79" s="4" t="n"/>
     </row>
     <row r="80" ht="32" customHeight="1">
@@ -3774,9 +4270,13 @@
           <t>Ding 等 - 2021 - The effect of socioeconomic disparities on prefrontal activation in initiating joint attention A fu.pdf</t>
         </is>
       </c>
-      <c r="I80" s="2" t="n"/>
-      <c r="J80" s="2" t="n"/>
-      <c r="K80" s="4" t="n"/>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="4" t="inlineStr"/>
       <c r="L80" s="4" t="n"/>
     </row>
     <row r="81" ht="32" customHeight="1">
@@ -3814,9 +4314,13 @@
           <t>Turesky 等 - 2019 - The relationship between biological and psychosocial risk factors and resting-state functional conne.pdf</t>
         </is>
       </c>
-      <c r="I81" s="2" t="n"/>
-      <c r="J81" s="2" t="n"/>
-      <c r="K81" s="4" t="n"/>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr"/>
       <c r="L81" s="4" t="n"/>
     </row>
     <row r="82" ht="32" customHeight="1">
@@ -3854,9 +4358,13 @@
           <t>Chung 等 - 2026 - Income insufficiency impacts early brain development in infants facing increased psychosocial advers.pdf</t>
         </is>
       </c>
-      <c r="I82" s="2" t="n"/>
-      <c r="J82" s="2" t="n"/>
-      <c r="K82" s="4" t="n"/>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="4" t="inlineStr"/>
       <c r="L82" s="4" t="n"/>
     </row>
     <row r="83" ht="32" customHeight="1">
@@ -3894,9 +4402,13 @@
           <t>Xie 等 - 2019 - Growth faltering is associated with altered brain functional connectivity and cognitive outcomes in.pdf</t>
         </is>
       </c>
-      <c r="I83" s="2" t="n"/>
-      <c r="J83" s="2" t="n"/>
-      <c r="K83" s="4" t="n"/>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr"/>
       <c r="L83" s="4" t="n"/>
     </row>
     <row r="84" ht="32" customHeight="1">
@@ -3934,9 +4446,21 @@
           <t>Willner 等 - 2015 - Relevance of a neurophysiological marker of attention allocation for children’s learning-related beh.pdf</t>
         </is>
       </c>
-      <c r="I84" s="2" t="n"/>
-      <c r="J84" s="2" t="n"/>
-      <c r="K84" s="4" t="n"/>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L84" s="4" t="n"/>
     </row>
     <row r="85" ht="32" customHeight="1">
@@ -3974,9 +4498,21 @@
           <t>Katus 等 - 2019 - Implementing neuroimaging and eye tracking methods to assess neurocognitive development of young inf.pdf</t>
         </is>
       </c>
-      <c r="I85" s="2" t="n"/>
-      <c r="J85" s="2" t="n"/>
-      <c r="K85" s="4" t="n"/>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>教育变量无独立效应</t>
+        </is>
+      </c>
       <c r="L85" s="4" t="n"/>
     </row>
     <row r="86" ht="32" customHeight="1">
@@ -4014,9 +4550,13 @@
           <t>Leverett 等 - 2025 - Associations between parenting and cognitive and language abilities at 2 years of age depend on pren.pdf</t>
         </is>
       </c>
-      <c r="I86" s="2" t="n"/>
-      <c r="J86" s="2" t="n"/>
-      <c r="K86" s="4" t="n"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="4" t="inlineStr"/>
       <c r="L86" s="4" t="n"/>
     </row>
     <row r="87" ht="32" customHeight="1">
@@ -4054,9 +4594,13 @@
           <t>Tonér 等 - 2021 - Selective auditory attention associated with language skills but not with executive functions in swe.pdf</t>
         </is>
       </c>
-      <c r="I87" s="2" t="n"/>
-      <c r="J87" s="2" t="n"/>
-      <c r="K87" s="4" t="n"/>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="4" t="inlineStr"/>
       <c r="L87" s="4" t="n"/>
     </row>
     <row r="88" ht="32" customHeight="1">
@@ -4094,9 +4638,13 @@
           <t>Leverett 等 - 2026 - Neonatal brain volumes and early parenting behavior as mediators in associations between prenatal so.pdf</t>
         </is>
       </c>
-      <c r="I88" s="2" t="n"/>
-      <c r="J88" s="2" t="n"/>
-      <c r="K88" s="4" t="n"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="4" t="inlineStr"/>
       <c r="L88" s="4" t="n"/>
     </row>
     <row r="89" ht="32" customHeight="1">
@@ -4134,9 +4682,13 @@
           <t>Aghamohammadi-Sereshki 等 - 2026 - A longitudinal study of children's hippocampal development Investigating maternal physical activity.pdf</t>
         </is>
       </c>
-      <c r="I89" s="2" t="n"/>
-      <c r="J89" s="2" t="n"/>
-      <c r="K89" s="4" t="n"/>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="4" t="inlineStr"/>
       <c r="L89" s="4" t="n"/>
     </row>
     <row r="90" ht="32" customHeight="1">
@@ -4174,9 +4726,13 @@
           <t>Derauf 等 - 2012 - Subcortical and cortical structural central nervous system changes and attention processing deficits.pdf</t>
         </is>
       </c>
-      <c r="I90" s="2" t="n"/>
-      <c r="J90" s="2" t="n"/>
-      <c r="K90" s="4" t="n"/>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="4" t="inlineStr"/>
       <c r="L90" s="4" t="n"/>
     </row>
     <row r="91" ht="32" customHeight="1">
@@ -4214,10 +4770,26 @@
           <t>2026_Parallel contributions ofsocioeconomic status and bilingualexperiences.pdf</t>
         </is>
       </c>
-      <c r="I91" s="2" t="n"/>
-      <c r="J91" s="2" t="n"/>
-      <c r="K91" s="4" t="n"/>
-      <c r="L91" s="4" t="n"/>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>同#53</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>原序号102</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="32" customHeight="1">
       <c r="A92" s="2" t="n">
@@ -4254,9 +4826,21 @@
           <t>Leverett 等 - 2026 - Neonatal brain volumes and early parenting behavior as mediators in associations between prenatal so.pdf</t>
         </is>
       </c>
-      <c r="I92" s="2" t="n"/>
-      <c r="J92" s="2" t="n"/>
-      <c r="K92" s="4" t="n"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>同#87（同一数据集）</t>
+        </is>
+      </c>
       <c r="L92" s="4" t="n"/>
     </row>
     <row r="93" ht="32" customHeight="1">
@@ -4294,10 +4878,22 @@
           <t>Pietto 等 - 2018 - Enhancement of inhibitory control in a sample of preschoolers from poor homes after cognitive traini.pdf</t>
         </is>
       </c>
-      <c r="I93" s="2" t="n"/>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>不确定</t>
+        </is>
+      </c>
       <c r="J93" s="2" t="n"/>
-      <c r="K93" s="4" t="n"/>
-      <c r="L93" s="4" t="n"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>干预+ERP研究，需核查全文是否报告父母教育独立效应</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>原序号105</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="32" customHeight="1">
       <c r="A94" s="2" t="n">
@@ -4334,10 +4930,26 @@
           <t>Tomalski 等 - 2013 - Socioeconomic status and functional brain development – associations in early infancy.pdf</t>
         </is>
       </c>
-      <c r="I94" s="2" t="n"/>
-      <c r="J94" s="2" t="n"/>
-      <c r="K94" s="4" t="n"/>
-      <c r="L94" s="4" t="n"/>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>同#38（同一文献重复收录）</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>原序号106</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="32" customHeight="1">
       <c r="A95" s="2" t="n">
@@ -4374,9 +4986,21 @@
           <t>Sheinkopf 等 - 2009 - Functional MRI and response inhibition in children exposed to cocaine in utero.pdf</t>
         </is>
       </c>
-      <c r="I95" s="2" t="n"/>
-      <c r="J95" s="2" t="n"/>
-      <c r="K95" s="4" t="n"/>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>E7</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>同#55（同一文献重复收录）</t>
+        </is>
+      </c>
       <c r="L95" s="4" t="n"/>
     </row>
     <row r="96" ht="32" customHeight="1">
@@ -4414,9 +5038,21 @@
           <t>Greenberg - 1969 - Developmental and clinical correlates of cerebral dysrythmia.pdf</t>
         </is>
       </c>
-      <c r="I96" s="2" t="n"/>
-      <c r="J96" s="2" t="n"/>
-      <c r="K96" s="4" t="n"/>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L96" s="4" t="n"/>
     </row>
     <row r="97" ht="32" customHeight="1">
@@ -4454,9 +5090,13 @@
           <t>2025_The longitudinal interplay ofprint exposure and auditory brainresponses.pdf</t>
         </is>
       </c>
-      <c r="I97" s="2" t="n"/>
-      <c r="J97" s="2" t="n"/>
-      <c r="K97" s="4" t="n"/>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="4" t="inlineStr"/>
       <c r="L97" s="4" t="n"/>
     </row>
     <row r="98" ht="32" customHeight="1">
@@ -4494,9 +5134,21 @@
           <t>Leijser 等 - 2018 - Imaging evidence of the effect of socio-economic status on brain structure and development.pdf</t>
         </is>
       </c>
-      <c r="I98" s="2" t="n"/>
-      <c r="J98" s="2" t="n"/>
-      <c r="K98" s="4" t="n"/>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>教育变量无独立效应</t>
+        </is>
+      </c>
       <c r="L98" s="4" t="n"/>
     </row>
     <row r="99" ht="32" customHeight="1">
@@ -4534,9 +5186,21 @@
           <t>Kelly和Li - 2019 - Poverty, toxic stress, and education in children born preterm.pdf</t>
         </is>
       </c>
-      <c r="I99" s="2" t="n"/>
-      <c r="J99" s="2" t="n"/>
-      <c r="K99" s="4" t="n"/>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>E3</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>无神经测量指标</t>
+        </is>
+      </c>
       <c r="L99" s="4" t="n"/>
     </row>
     <row r="100" ht="32" customHeight="1">
@@ -4574,9 +5238,21 @@
           <t>Chernick 等 - 1983 - Effects of maternal alcohol intake and smoking on neonatal electroencephalogram and anthropometric m.pdf</t>
         </is>
       </c>
-      <c r="I100" s="2" t="n"/>
-      <c r="J100" s="2" t="n"/>
-      <c r="K100" s="4" t="n"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L100" s="4" t="n"/>
     </row>
     <row r="101" ht="32" customHeight="1">
@@ -4614,9 +5290,13 @@
           <t>Romeo 等 - 2021 - Neuroplasticity associated with changes in conversational turn-taking following a family-based inter.pdf</t>
         </is>
       </c>
-      <c r="I101" s="2" t="n"/>
-      <c r="J101" s="2" t="n"/>
-      <c r="K101" s="4" t="n"/>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="4" t="inlineStr"/>
       <c r="L101" s="4" t="n"/>
     </row>
     <row r="102" ht="32" customHeight="1">
@@ -4654,9 +5334,21 @@
           <t>2021_Timing-specific associations between income-to-needs ratio and hippocampal.pdf</t>
         </is>
       </c>
-      <c r="I102" s="2" t="n"/>
-      <c r="J102" s="2" t="n"/>
-      <c r="K102" s="4" t="n"/>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>PDF不存在</t>
+        </is>
+      </c>
       <c r="L102" s="4" t="n"/>
     </row>
     <row r="103" ht="32" customHeight="1">
@@ -4694,9 +5386,13 @@
           <t>Brandes-Aitken 等 - 2024 - Maternal heart rate variability at 3-months postpartum is associated with maternal mental health and.pdf</t>
         </is>
       </c>
-      <c r="I103" s="2" t="n"/>
-      <c r="J103" s="2" t="n"/>
-      <c r="K103" s="4" t="n"/>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="4" t="inlineStr"/>
       <c r="L103" s="4" t="n"/>
     </row>
     <row r="104" ht="32" customHeight="1">
@@ -4734,9 +5430,13 @@
           <t>Simon 等 - 2021 - Socioeconomic factors, stress, hair cortisol, and white matter microstructure in children.pdf</t>
         </is>
       </c>
-      <c r="I104" s="2" t="n"/>
-      <c r="J104" s="2" t="n"/>
-      <c r="K104" s="4" t="n"/>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="4" t="inlineStr"/>
       <c r="L104" s="4" t="n"/>
     </row>
     <row r="105" ht="32" customHeight="1">
@@ -4774,9 +5474,13 @@
           <t>Ursache 等 - 2016 - Socioeconomic status, white matter, and executive function in children.pdf</t>
         </is>
       </c>
-      <c r="I105" s="2" t="n"/>
-      <c r="J105" s="2" t="n"/>
-      <c r="K105" s="4" t="n"/>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="4" t="inlineStr"/>
       <c r="L105" s="4" t="n"/>
     </row>
     <row r="106" ht="32" customHeight="1">
@@ -4814,9 +5518,13 @@
           <t>Faghiri 等 - 2019 - Brain development includes linear and multiple nonlinear trajectories A cross-sectional resting-sta.pdf</t>
         </is>
       </c>
-      <c r="I106" s="2" t="n"/>
-      <c r="J106" s="2" t="n"/>
-      <c r="K106" s="4" t="n"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr"/>
       <c r="L106" s="4" t="n"/>
     </row>
     <row r="107" ht="32" customHeight="1">
@@ -4854,9 +5562,21 @@
           <t>Willner 等 - 2020 - Neurophysiological evidence for distinct biases in emotional face processing associated with interna.pdf</t>
         </is>
       </c>
-      <c r="I107" s="2" t="n"/>
-      <c r="J107" s="2" t="n"/>
-      <c r="K107" s="4" t="n"/>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>无父母教育变量</t>
+        </is>
+      </c>
       <c r="L107" s="4" t="n"/>
     </row>
     <row r="108" ht="32" customHeight="1">
@@ -4894,9 +5614,13 @@
           <t>Stevens 等 - 2015 - Atypical auditory refractory periods in children from lower socio-economic status backgrounds ERP e.pdf</t>
         </is>
       </c>
-      <c r="I108" s="2" t="n"/>
-      <c r="J108" s="2" t="n"/>
-      <c r="K108" s="4" t="n"/>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="4" t="inlineStr"/>
       <c r="L108" s="4" t="n"/>
     </row>
     <row r="109" ht="32" customHeight="1">
@@ -4934,9 +5658,21 @@
           <t>LeWinn 等 - 2017 - Sample composition alters associations between age and brain structure.pdf</t>
         </is>
       </c>
-      <c r="I109" s="2" t="n"/>
-      <c r="J109" s="2" t="n"/>
-      <c r="K109" s="4" t="n"/>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>年龄不符</t>
+        </is>
+      </c>
       <c r="L109" s="4" t="n"/>
     </row>
     <row r="110" ht="32" customHeight="1">
@@ -4974,9 +5710,13 @@
           <t>Lange 等 - 2010 - Associations between IQ, total and regional brain volumes, and demography in a large normative sampl.pdf</t>
         </is>
       </c>
-      <c r="I110" s="2" t="n"/>
-      <c r="J110" s="2" t="n"/>
-      <c r="K110" s="4" t="n"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>纳入</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="inlineStr"/>
+      <c r="K110" s="4" t="inlineStr"/>
       <c r="L110" s="4" t="n"/>
     </row>
   </sheetData>

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>教育变量无独立效应</t>
+          <t>综述文章（REVIEW ARTICLE），不是原始研究</t>
         </is>
       </c>
       <c r="L13" s="4" t="n"/>
@@ -1477,12 +1477,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>教育变量无独立效应</t>
+          <t>综述文章（Seminars in F&amp;NM），不是原始研究</t>
         </is>
       </c>
       <c r="L19" s="4" t="n"/>

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -3632,18 +3632,14 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>不确定</t>
+          <t>纳入</t>
         </is>
       </c>
       <c r="J66" s="2" t="n"/>
-      <c r="K66" s="4" t="inlineStr">
-        <is>
-          <t>E7参照错误（非重复文献），需全文核查父母教育是否独立报告</t>
-        </is>
-      </c>
+      <c r="K66" s="4" t="n"/>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>原序号73</t>
+          <t>oo核查：fNIRS+SES主暴露，纳入</t>
         </is>
       </c>
     </row>
@@ -4880,18 +4876,22 @@
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>不确定</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
-          <t>干预+ERP研究，需核查全文是否报告父母教育独立效应</t>
+          <t>干预研究，父母教育仅作基线均衡检验，非主暴露</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>原序号105</t>
+          <t>oo核查确认</t>
         </is>
       </c>
     </row>

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -700,12 +700,24 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为白质发育预测阅读能力，SES/父母教育仅作协变量控制，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>oo数据提取阶段核查发现，CC提示</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="2" t="n">

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -1388,12 +1388,24 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为现金转移干预(RCT)，父母教育无独立效应量</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>oo系统排查修正</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="A18" s="2" t="n">
@@ -2180,12 +2192,24 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr"/>
-      <c r="K34" s="4" t="inlineStr"/>
-      <c r="L34" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为LI vs MI收入分组，父母教育仅作组间差异描述，未进入神经指标回归模型</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>oo系统排查修正</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="2" t="n">
@@ -2356,12 +2380,24 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr"/>
-      <c r="K38" s="4" t="inlineStr"/>
-      <c r="L38" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为产前抑郁，母亲教育仅作协变量控制，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>oo系统排查修正</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="32" customHeight="1">
       <c r="A39" s="2" t="n">
@@ -3332,12 +3368,24 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="4" t="inlineStr"/>
-      <c r="L59" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为生长迟缓(HAZ)，SES/教育仅作协变量控制</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>oo系统排查修正</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="32" customHeight="1">
       <c r="A60" s="2" t="n">
@@ -3468,12 +3516,24 @@
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr"/>
-      <c r="K62" s="4" t="inlineStr"/>
-      <c r="L62" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为产前逆境综合评分，父母教育无独立效应量</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>oo系统排查修正</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="32" customHeight="1">
       <c r="A63" s="2" t="n">
@@ -4008,12 +4068,24 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr"/>
-      <c r="K74" s="4" t="inlineStr"/>
-      <c r="L74" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>父母教育为parental ecology复合因子之一，无独立beta系数</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>oo系统排查修正</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="32" customHeight="1">
       <c r="A75" s="2" t="n">
@@ -4192,12 +4264,24 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr"/>
-      <c r="K78" s="4" t="inlineStr"/>
-      <c r="L78" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为income-to-needs，父母教育仅作协变量控制</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>oo系统排查修正</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="32" customHeight="1">
       <c r="A79" s="2" t="n">
@@ -5400,12 +5484,24 @@
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr"/>
-      <c r="K103" s="4" t="inlineStr"/>
-      <c r="L103" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>标题明确"not parental education"，教育效应不显著(r=0.13, p=0.10)</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>oo系统排查修正</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="32" customHeight="1">
       <c r="A104" s="2" t="n">

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -656,12 +656,24 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为家庭收入/贫困(income-to-needs)，父母教育仅作协变量控制，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="2" t="n">
@@ -1004,12 +1016,24 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为产前可卡因暴露(PCE)，母亲教育仅作协变量，原文明确"No significant main effects of maternal education were detected"</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>oo数据提取阶段全文核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="2" t="n">
@@ -1636,12 +1660,24 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="4" t="inlineStr"/>
-      <c r="L22" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为产前逆境综合评分，教育是其中一个成分，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>oo全文核查最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="2" t="n">
@@ -1768,12 +1804,24 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr"/>
-      <c r="L25" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>明确"Parental education was not used as a predictor"</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="32" customHeight="1">
       <c r="A26" s="2" t="n">
@@ -1920,12 +1968,24 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr"/>
-      <c r="K28" s="4" t="inlineStr"/>
-      <c r="L28" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>教育交互项p=0.459，无显著独立效应</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>oo全文核查最终修正-无显著效应或主暴露不符</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="2" t="n">
@@ -2008,12 +2068,24 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr"/>
-      <c r="K30" s="4" t="inlineStr"/>
-      <c r="L30" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为家庭收入不稳定性，教育仅人口学描述，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -2148,12 +2220,24 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr"/>
-      <c r="K33" s="4" t="inlineStr"/>
-      <c r="L33" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>随机干预研究，主暴露为认知体验干预，父母教育无独立效应量</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>oo全文核查最终修正-无显著效应或主暴露不符</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="2" t="n">
@@ -2336,12 +2420,24 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr"/>
-      <c r="K37" s="4" t="inlineStr"/>
-      <c r="L37" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>教育仅在Discussion引用他人研究，无独立统计值，主暴露为SES综合</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="2" t="n">
@@ -2480,12 +2576,24 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr"/>
-      <c r="K40" s="4" t="inlineStr"/>
-      <c r="L40" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>教育作协变量被排除，与阅读质量无显著相关(p&gt;.05)</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="32" customHeight="1">
       <c r="A41" s="2" t="n">
@@ -2524,12 +2632,24 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr"/>
-      <c r="K41" s="4" t="inlineStr"/>
-      <c r="L41" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>教育作为SES评分乘法公式的一部分，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="2" t="n">
@@ -2568,12 +2688,24 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr"/>
-      <c r="K42" s="4" t="inlineStr"/>
-      <c r="L42" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>教育是社会劣势复合评分(PSD)成分之一，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="32" customHeight="1">
       <c r="A43" s="2" t="n">
@@ -2612,12 +2744,24 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr"/>
-      <c r="K43" s="4" t="inlineStr"/>
-      <c r="L43" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>教育是PSD复合评分成分之一，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="32" customHeight="1">
       <c r="A44" s="2" t="n">
@@ -2700,12 +2844,24 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr"/>
-      <c r="K45" s="4" t="inlineStr"/>
-      <c r="L45" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为家庭贫困/脑发育速率，教育仅描述性，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="32" customHeight="1">
       <c r="A46" s="2" t="n">
@@ -2744,12 +2900,24 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr"/>
-      <c r="K46" s="4" t="inlineStr"/>
-      <c r="L46" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>标题明确"prenatal family income, but NOT parental education"，教育效应不显著</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>oo全文核查最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="2" t="n">
@@ -2932,12 +3100,24 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr"/>
-      <c r="K50" s="4" t="inlineStr"/>
-      <c r="L50" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>教育仅作协变量控制，主暴露为母乳喂养与脑结构</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="32" customHeight="1">
       <c r="A51" s="2" t="n">
@@ -3028,12 +3208,24 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr"/>
-      <c r="K52" s="4" t="inlineStr"/>
-      <c r="L52" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>教育仅描述性列出(years)，无独立统计分析</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="32" customHeight="1">
       <c r="A53" s="2" t="n">
@@ -3120,14 +3312,22 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr"/>
-      <c r="K54" s="4" t="inlineStr"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为围手术期病程，教育无实质统计分析</t>
+        </is>
+      </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>原序号107</t>
+          <t>oo全文阅读系统核查修正</t>
         </is>
       </c>
     </row>
@@ -3272,12 +3472,24 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr"/>
-      <c r="K57" s="4" t="inlineStr"/>
-      <c r="L57" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>教育作为SES背景描述，无独立效应量，主暴露为母亲压力与语言行为</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="2" t="n">
@@ -3424,14 +3636,22 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr"/>
-      <c r="K60" s="4" t="inlineStr"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>原文明确"no associations between income-to-needs or maternal education and brain structure"</t>
+        </is>
+      </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>原序号103</t>
+          <t>oo全文阅读系统核查修正</t>
         </is>
       </c>
     </row>
@@ -3472,12 +3692,24 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="4" t="inlineStr"/>
-      <c r="L61" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>教育仅背景引用，无独立统计值</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="32" customHeight="1">
       <c r="A62" s="2" t="n">
@@ -3572,12 +3804,24 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr"/>
-      <c r="K63" s="4" t="inlineStr"/>
-      <c r="L63" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>教育效应t(254)=0.79, p=0.43，无显著关联</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>oo全文核查最终修正-无显著效应或主暴露不符</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="2" t="n">
@@ -3616,12 +3860,24 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr"/>
-      <c r="K64" s="4" t="inlineStr"/>
-      <c r="L64" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>原文明确"no significant main effects of parental education"</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="32" customHeight="1">
       <c r="A65" s="2" t="n">
@@ -3704,14 +3960,22 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为LI vs MI收入分组，父母教育仅作组间差异描述，未进入神经指标回归模型</t>
+        </is>
+      </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>oo核查：fNIRS+SES主暴露，纳入</t>
+          <t>oo全文核查最终修正</t>
         </is>
       </c>
     </row>
@@ -3804,12 +4068,24 @@
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr"/>
-      <c r="K68" s="4" t="inlineStr"/>
-      <c r="L68" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>教育是Hollingshead SES复合评分成分，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="32" customHeight="1">
       <c r="A69" s="2" t="n">
@@ -3848,12 +4124,24 @@
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr"/>
-      <c r="K69" s="4" t="inlineStr"/>
-      <c r="L69" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>教育是SES复合评分成分，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="2" t="n">
@@ -3892,12 +4180,24 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr"/>
-      <c r="K70" s="4" t="inlineStr"/>
-      <c r="L70" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>原文明确"no influence of maternal education"</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="32" customHeight="1">
       <c r="A71" s="2" t="n">
@@ -3936,12 +4236,24 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr"/>
-      <c r="K71" s="4" t="inlineStr"/>
-      <c r="L71" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>教育仅作为贫困指标之一列出，无独立统计值</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="32" customHeight="1">
       <c r="A72" s="2" t="n">
@@ -3980,12 +4292,24 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr"/>
-      <c r="K72" s="4" t="inlineStr"/>
-      <c r="L72" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>教育仅描述性列出，无统计分析，主暴露为贫困/文化劣势</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="32" customHeight="1">
       <c r="A73" s="2" t="n">
@@ -4124,12 +4448,24 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr"/>
-      <c r="K75" s="4" t="inlineStr"/>
-      <c r="L75" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>教育仅作SES背景描述，主暴露为认知刺激中介，无父母教育独立效应量</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="32" customHeight="1">
       <c r="A76" s="2" t="n">
@@ -4452,12 +4788,24 @@
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr"/>
-      <c r="K82" s="4" t="inlineStr"/>
-      <c r="L82" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为收入不足，教育仅背景描述，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="32" customHeight="1">
       <c r="A83" s="2" t="n">
@@ -4496,12 +4844,24 @@
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr"/>
-      <c r="K83" s="4" t="inlineStr"/>
-      <c r="L83" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>教育仅参考文献引用，主暴露为生长迟缓，无实质分析</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="32" customHeight="1">
       <c r="A84" s="2" t="n">
@@ -4644,12 +5004,24 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr"/>
-      <c r="K86" s="4" t="inlineStr"/>
-      <c r="L86" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>教育是PSD复合评分一部分，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="32" customHeight="1">
       <c r="A87" s="2" t="n">
@@ -4688,12 +5060,24 @@
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr"/>
-      <c r="K87" s="4" t="inlineStr"/>
-      <c r="L87" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>教育仅背景描述，主暴露为SES分组，无父母教育独立效应量</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="32" customHeight="1">
       <c r="A88" s="2" t="n">
@@ -4732,12 +5116,24 @@
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="4" t="inlineStr"/>
-      <c r="L88" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>同#85，教育是PSD复合评分一部分，无独立效应量</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="32" customHeight="1">
       <c r="A89" s="2" t="n">
@@ -4820,12 +5216,24 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr"/>
-      <c r="K90" s="4" t="inlineStr"/>
-      <c r="L90" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>教育仅作协变量控制，主暴露为早产/围产期因素</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="2" t="n">
@@ -5188,12 +5596,24 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr"/>
-      <c r="K97" s="4" t="inlineStr"/>
-      <c r="L97" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为印刷品接触量，教育仅机构名，无实质分析</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="32" customHeight="1">
       <c r="A98" s="2" t="n">
@@ -5388,12 +5808,24 @@
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="4" t="inlineStr"/>
-      <c r="L101" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为对话轮次干预，教育仅机构名，无实质分析</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="32" customHeight="1">
       <c r="A102" s="2" t="n">
@@ -5628,12 +6060,24 @@
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr"/>
-      <c r="K106" s="4" t="inlineStr"/>
-      <c r="L106" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>教育r=0.05, p=0.3，无显著效应</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>oo全文阅读系统核查修正</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="32" customHeight="1">
       <c r="A107" s="2" t="n">

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -2332,11 +2332,19 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr"/>
-      <c r="K35" s="4" t="inlineStr"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为母亲皮质醇；母亲教育未测量，完全不在模型中，无独立效应量</t>
+        </is>
+      </c>
       <c r="L35" s="4" t="n"/>
     </row>
     <row r="36" ht="32" customHeight="1">
@@ -5172,11 +5180,19 @@
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr"/>
-      <c r="K89" s="4" t="inlineStr"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为母亲体力活动；教育无显著效应（no significant correlation with hippocampal development）</t>
+        </is>
+      </c>
       <c r="L89" s="4" t="n"/>
     </row>
     <row r="90" ht="32" customHeight="1">

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -1716,12 +1716,24 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
-      <c r="L23" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为Total SES复合得分，未独立报告父母教育的效应量</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>oo全文核查最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="2" t="n">

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -2090,12 +2090,12 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>主暴露为家庭收入不稳定性，教育仅人口学描述，无独立效应量</t>
+          <t>主暴露为家庭收入不稳定性，教育仅作为人口学描述</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>oo全文阅读系统核查修正</t>
+          <t>oo全文核查最终修正</t>
         </is>
       </c>
     </row>
@@ -2146,10 +2146,14 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>无父母教育变量</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="n"/>
+          <t>主暴露为围产期脑病患儿MRI成功率影响因素，无父母教育独立效应</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>oo全文核查最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="2" t="n">
@@ -2188,12 +2192,24 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr"/>
-      <c r="K32" s="4" t="inlineStr"/>
-      <c r="L32" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>主暴露为慢性炎症/贫困，教育仅列为人口学统计</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>oo全文核查最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="2" t="n">
@@ -2242,12 +2258,12 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>随机干预研究，主暴露为认知体验干预，父母教育无独立效应量</t>
+          <t>RCT研究，主暴露为早期认知干预（随机分配），父母教育仅为协变量</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>oo全文核查最终修正-无显著效应或主暴露不符</t>
+          <t>oo全文核查最终修正</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2314,12 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>主暴露为LI vs MI收入分组，父母教育仅作组间差异描述，未进入神经指标回归模型</t>
+          <t>主暴露为SES动态发展，教育仅为人口学背景</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>oo系统排查修正</t>
+          <t>oo全文核查最终修正</t>
         </is>
       </c>
     </row>

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -2412,12 +2412,24 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr"/>
-      <c r="K36" s="4" t="inlineStr"/>
-      <c r="L36" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>P3b主效应为收入，原文明确教育在高收入组无独立效应</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>oo全文精读最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="2" t="n">
@@ -3048,12 +3060,24 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="4" t="inlineStr"/>
-      <c r="L48" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>原文明确未发现gamma power与parental education的相关</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>oo全文精读最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="2" t="n">
@@ -4780,12 +4804,24 @@
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr"/>
-      <c r="K81" s="4" t="inlineStr"/>
-      <c r="L81" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>教育仅作为儿童发展危险因素列举，无独立统计值</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>oo全文精读最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="32" customHeight="1">
       <c r="A82" s="2" t="n">
@@ -6016,12 +6052,24 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="4" t="inlineStr"/>
-      <c r="L104" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>原文明确"neither family ITN nor parental education was significantly associated"</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>oo全文精读最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="32" customHeight="1">
       <c r="A105" s="2" t="n">
@@ -6212,12 +6260,24 @@
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr"/>
-      <c r="K108" s="4" t="inlineStr"/>
-      <c r="L108" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>原文明确"no significant differences between higher and lower maternal education groups"</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>oo全文精读最终修正</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="32" customHeight="1">
       <c r="A109" s="2" t="n">

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -2580,12 +2580,24 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
-      <c r="L39" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>原文明确maternal/paternal education效应仅为"near-significant"（不显著），无独立效应量</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>oo最终全文精读修正</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="2" t="n">
@@ -3116,12 +3128,24 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr"/>
-      <c r="K49" s="4" t="inlineStr"/>
-      <c r="L49" s="4" t="n"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>教育仅用于SES分组描述，无独立统计分析</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>oo最终全文精读修正</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="2" t="n">
@@ -3324,14 +3348,22 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr"/>
-      <c r="K53" s="4" t="inlineStr"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>原文明确"did not see any association of ... maternal education"</t>
+        </is>
+      </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>原序号106</t>
+          <t>oo最终全文精读修正</t>
         </is>
       </c>
     </row>

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -1726,7 +1726,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>主暴露为Total SES复合得分，未独立报告父母教育的效应量</t>
+          <t>仅报告复合SES分，无父母教育独立效应</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>主暴露为家庭收入不稳定性，教育仅作为人口学描述</t>
+          <t>主暴露为家庭收入不稳定性，父母教育仅人口学描述，无独立效应量</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>主暴露为围产期脑病患儿MRI成功率影响因素，无父母教育独立效应</t>
+          <t>主暴露为围产期脑病MRI成功率，无父母教育独立效应</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>主暴露为慢性炎症/贫困，教育仅列为人口学统计</t>
+          <t>主暴露为慢性炎症/贫困，父母教育仅人口学背景</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>RCT研究，主暴露为早期认知干预（随机分配），父母教育仅为协变量</t>
+          <t>RCT，主暴露为认知干预，父母教育仅协变量</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>主暴露为SES动态发展，教育仅为人口学背景</t>
+          <t>主暴露为SES动态发展，父母教育无独立效应量</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>P3b主效应为收入，原文明确教育在高收入组无独立效应</t>
+          <t>P3b主效应为收入，父母教育无显著独立效应</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>原文明确maternal/paternal education效应仅为"near-significant"（不显著），无独立效应量</t>
+          <t>教育效应仅near-significant，未达显著</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>原文明确未发现gamma power与parental education的相关</t>
+          <t>原文明确gamma power与父母教育无相关</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>教育仅用于SES分组描述，无独立统计分析</t>
+          <t>父母教育仅用于SES分组，无独立统计分析</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>原文明确"did not see any association of ... maternal education"</t>
+          <t>原文明确did not see any association of maternal education</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>教育仅作为儿童发展危险因素列举，无独立统计值</t>
+          <t>父母教育仅作为危险因素列举，无独立统计值</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="K104" s="4" t="inlineStr">
         <is>
-          <t>原文明确"neither family ITN nor parental education was significantly associated"</t>
+          <t>原文明确neither parental education was significantly associated</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>原文明确"no significant differences between higher and lower maternal education groups"</t>
+          <t>原文明确no significant differences between education groups</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">

--- a/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
+++ b/projects/paper-02/03-screen/数据_5_第三轮全文筛选.xlsx
@@ -4792,11 +4792,19 @@
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>纳入</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr"/>
-      <c r="K80" s="4" t="inlineStr"/>
+          <t>排除</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>主统计为SES分组ANOVA，MEL与SES r=0.948（共线），教育无独立回归系数，composite-inseparable</t>
+        </is>
+      </c>
       <c r="L80" s="4" t="n"/>
     </row>
     <row r="81" ht="32" customHeight="1">
